--- a/common/excel/xls/skillStone.xlsx
+++ b/common/excel/xls/skillStone.xlsx
@@ -584,9 +584,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="61.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -598,139 +598,246 @@
     <col min="8" max="8" width="14.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+    <row r="1" spans="1:1" ns3:dyDescent="0.3">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>convert(skillStone.txt,ActiveSkillStoneConf.pb,ActiveSkillStoneConf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ns3:dyDescent="0.3">
+      <c r="A2" t="inlineStr" s="1">
+        <is>
+          <t>ActiveSkillStoneId</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="1">
+        <is>
+          <t>ActiveSkillStoneCode</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="1">
+        <is>
+          <t>ActiveSkillStoneName</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="1">
+        <is>
+          <t>ActiveSkillStoneDesc</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="1">
+        <is>
+          <t>SkillEffectName</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="1">
+        <is>
+          <t>SkillColor</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="1">
+        <is>
+          <t>SkillCastType</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="1">
+        <is>
+          <t>SkillTags</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="1">
+        <is>
+          <t>SkillShapeType</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ns3:dyDescent="0.3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>火球术</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>发射一枚火球，命中时爆炸造成范围火焰伤害</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FireballCast</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ns3:dyDescent="0.3">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>frost_nova</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>冰霜新星</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>在周围释放冰霜爆炸，冻结附近敌人</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FrostNovaBurst</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ns3:dyDescent="0.3">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>blink</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>闪现</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>瞬间移动到目标位置</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BlinkFlash</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ns3:dyDescent="0.3">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>heavy_strike</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>重击</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>用沉重一击打击单体目标</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HeavyStrikeSlash</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
